--- a/smartshop/EvidenceBasedAdaptiveUI/reports/MoodOverrides/mood_overrides.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/MoodOverrides/mood_overrides.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,24 +502,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.4545</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.454545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.045</v>
+        <v>0.044643</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -530,38 +530,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>desktop_filter_location</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bold Large (Price is the most prominent element)</t>
+          <t>Top Bar (Filters displayed across the top)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>With Savings Highlighted (Shows discount amount prominently)</t>
+          <t>Sidebar Left (Permanent filter panel on the left side)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3889</v>
+        <v>0.4091</v>
       </c>
       <c r="G3" t="n">
-        <v>0.388889</v>
+        <v>0.409091</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035</v>
+        <v>0.040179</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -572,34 +572,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>desktop_grid_pref</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4 Columns (Compact view, many items visible at once)</t>
+          <t>Sidebar (Permanent navigation panel on the left)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3 Columns (Balanced view, moderate item size)</t>
+          <t>Top Bar (Categories always visible across the top)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333</v>
+        <v>0.3636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.333333</v>
+        <v>0.363636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>0.035714</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -614,30 +614,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
+          <t>Bold Large (Price is the most prominent element)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2778</v>
+        <v>0.3636</v>
       </c>
       <c r="G5" t="n">
-        <v>0.277778</v>
+        <v>0.363636</v>
       </c>
       <c r="H5" t="n">
-        <v>0.025</v>
+        <v>0.035714</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -651,35 +651,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Excited</t>
+          <t>Bored</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+          <t>Cool Blues (Blues and grays - calm and trustworthy)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.2727</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.272727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04</v>
+        <v>0.026786</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -698,34 +698,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Balanced (50% images, 50% text - equal emphasis)</t>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Image-focused (80% images, 20% text - highly visual)</t>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.035</v>
+        <v>0.035714</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -740,30 +740,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
+          <t>Balanced (50% images, 50% text - equal emphasis)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>Image-focused (80% images, 20% text - highly visual)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.025</v>
+        <v>0.03125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -782,17 +782,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
+          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Both (Show both stock and time based urgency)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -805,11 +805,11 @@
         <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.025</v>
+        <v>0.022321</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -819,43 +819,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Excited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Collapsible (Search bar that expands when clicked)</t>
+          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Always Visible Top (Large, prominent search bar always shown)</t>
+          <t>Both (Show both stock and time based urgency)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7647</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.764706</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.065</v>
+        <v>0.022321</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP, Association Rules</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -866,38 +866,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_search_visibility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Progress Bar (Multi step with visual progress indicator)</t>
+          <t>Collapsible (Search bar that expands when clicked)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>One Page (All checkout steps on a single scrolling page)</t>
+          <t>Always Visible Top (Large, prominent search bar always shown)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.588235</v>
+        <v>0.764706</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP, Association Rules</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -908,34 +908,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>desktop_filter_location</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Top Bar (Filters displayed across the top)</t>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sidebar Left (Permanent filter panel on the left side)</t>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4706</v>
+        <v>0.55</v>
       </c>
       <c r="G12" t="n">
-        <v>0.470588</v>
+        <v>0.55</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04</v>
+        <v>0.049107</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -964,24 +964,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4118</v>
+        <v>0.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.411765</v>
+        <v>0.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.035</v>
+        <v>0.035714</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, Random Forest</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -992,34 +992,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>desktop_grid_pref</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2 Columns (Large product images, fewer items per row)</t>
+          <t>Mega Menu (Dropdown with images and subcategories)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3 Columns (Balanced view, moderate item size)</t>
+          <t>Top Bar (Categories always visible across the top)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3529</v>
+        <v>0.35</v>
       </c>
       <c r="G14" t="n">
-        <v>0.352941</v>
+        <v>0.35</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03</v>
+        <v>0.03125</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3529</v>
+        <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>0.352941</v>
+        <v>0.35</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03</v>
+        <v>0.03125</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1071,35 +1071,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mobile_category_display</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Visual Grid (Category tiles with images)</t>
+          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dropdown Menu (Text-based dropdown list)</t>
+          <t>Both (Show both stock and time based urgency)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4935</v>
+        <v>0.25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.493506</v>
+        <v>0.25</v>
       </c>
       <c r="H16" t="n">
-        <v>0.19</v>
+        <v>0.022321</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1118,38 +1118,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>mobile_category_display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Progress Bar (Multi step with visual progress indicator)</t>
+          <t>Visual Grid (Category tiles with images)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>One Page (All checkout steps on a single scrolling page)</t>
+          <t>Dropdown Menu (Text-based dropdown list)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3896</v>
+        <v>0.4535</v>
       </c>
       <c r="G17" t="n">
-        <v>0.38961</v>
+        <v>0.453488</v>
       </c>
       <c r="H17" t="n">
-        <v>0.15</v>
+        <v>0.174107</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1160,34 +1160,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3896</v>
+        <v>0.3953</v>
       </c>
       <c r="G18" t="n">
-        <v>0.38961</v>
+        <v>0.395349</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0.151786</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1202,118 +1202,118 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>With Savings Highlighted (Shows discount amount prominently)</t>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2987</v>
+        <v>0.3837</v>
       </c>
       <c r="G19" t="n">
-        <v>0.298701</v>
+        <v>0.383721</v>
       </c>
       <c r="H19" t="n">
-        <v>0.115</v>
+        <v>0.147321</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Relaxed</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Collapsible (Search bar that expands when clicked)</t>
+          <t>Mega Menu (Dropdown with images and subcategories)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Always Visible Top (Large, prominent search bar always shown)</t>
+          <t>Top Bar (Categories always visible across the top)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4872</v>
+        <v>0.314</v>
       </c>
       <c r="G20" t="n">
-        <v>0.487179</v>
+        <v>0.313953</v>
       </c>
       <c r="H20" t="n">
-        <v>0.095</v>
+        <v>0.120536</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Relaxed</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>desktop_quick_view</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Modal Popup (Product details appear in a centered overlay)</t>
+          <t>With Comparison (Shows similar products' prices)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sidebar Slide (Details slide in from the right)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4103</v>
+        <v>0.2907</v>
       </c>
       <c r="G21" t="n">
-        <v>0.410256</v>
+        <v>0.290698</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08</v>
+        <v>0.111607</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1328,30 +1328,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>desktop_price_display</t>
+          <t>mobile_sticky_header</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
+          <t>No (Header scrolls away with content)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>With Savings Highlighted (Shows discount amount prominently)</t>
+          <t>Yes (Header stays at top while scrolling)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3077</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.307692</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06</v>
+        <v>0.09375</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1370,118 +1370,118 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>desktop_search_visibility</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
+          <t>Collapsible (Search bar that expands when clicked)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>Always Visible Top (Large, prominent search bar always shown)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2821</v>
+        <v>0.4762</v>
       </c>
       <c r="G23" t="n">
-        <v>0.282051</v>
+        <v>0.47619</v>
       </c>
       <c r="H23" t="n">
-        <v>0.055</v>
+        <v>0.089286</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stressed</t>
+          <t>Relaxed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>desktop_quick_view</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Balanced (50% images, 50% text - equal emphasis)</t>
+          <t>Modal Popup (Product details appear in a centered overlay)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Image-focused (80% images, 20% text - highly visual)</t>
+          <t>Sidebar Slide (Details slide in from the right)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5517</v>
+        <v>0.4286</v>
       </c>
       <c r="G24" t="n">
-        <v>0.551724</v>
+        <v>0.428571</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08</v>
+        <v>0.080357</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stressed</t>
+          <t>Relaxed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mobile_filter_location</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bottom Sheet (Slides up from bottom   mobile style)</t>
+          <t>Sidebar (Permanent navigation panel on the left)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Drawer Overlay (Slides in from the side when clicked)</t>
+          <t>Top Bar (Categories always visible across the top)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4828</v>
+        <v>0.3571</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482759</v>
+        <v>0.357143</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066964</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1491,77 +1491,77 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stressed</t>
+          <t>Relaxed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hero_banner_size</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Small Strip (Thin banner across the top)</t>
+          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Medium Split (Takes up half the screen)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4483</v>
+        <v>0.3095</v>
       </c>
       <c r="G26" t="n">
-        <v>0.448276</v>
+        <v>0.309524</v>
       </c>
       <c r="H26" t="n">
-        <v>0.065</v>
+        <v>0.058036</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, Random Forest</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stressed</t>
+          <t>Relaxed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mobile_product_card</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4483</v>
+        <v>0.2619</v>
       </c>
       <c r="G27" t="n">
-        <v>0.448276</v>
+        <v>0.261905</v>
       </c>
       <c r="H27" t="n">
-        <v>0.065</v>
+        <v>0.049107</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1580,34 +1580,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stock Numbers (Show "Only 3 left in stock")</t>
+          <t>Balanced (50% images, 50% text - equal emphasis)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Both (Show both stock and time based urgency)</t>
+          <t>Image-focused (80% images, 20% text - highly visual)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2759</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.275862</v>
+        <v>0.588235</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04</v>
+        <v>0.089286</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1622,38 +1622,206 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>desktop_grid_pref</t>
+          <t>mobile_filter_location</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>List View (One product per row with details on the side)</t>
+          <t>Bottom Sheet (Slides up from bottom   mobile style)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3 Columns (Balanced view, moderate item size)</t>
+          <t>Drawer Overlay (Slides in from the side when clicked)</t>
         </is>
       </c>
       <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.441176</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.066964</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mobile_product_card</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.411765</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Statistics, SHAP</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>desktop_category_display</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Text List (Simple text links)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Visual Grid (Category tiles with images)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.352941</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.053571</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>background_pref</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Light Gray (Soft, reduces eye strain)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Cream/Off-white (Warm, comfortable, paper-like)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.294118</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.044643</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>urgency_pref</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Both (Show both stock and time based urgency)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.2759</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.275862</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Random Forest, SHAP</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
+      <c r="F33" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.235294</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.035714</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
